--- a/All_Bioassays/continuous_no_high_outliers.xlsx
+++ b/All_Bioassays/continuous_no_high_outliers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4795f5e3347afba5/Desktop/Dissertation/Lake_Murray/2024-25_Lake_Murray_Bioassays/All_Bioassays/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{9888EFB7-0691-46D3-BE50-9C3319992C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F51F17F-26D6-457F-AAE5-A98DA6467277}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="8_{9888EFB7-0691-46D3-BE50-9C3319992C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A4C2EF5-8C5E-4E63-A6D1-F15C0445BEC5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{21FBA956-5CC7-4BE8-B4A1-5F975C966CBC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{21FBA956-5CC7-4BE8-B4A1-5F975C966CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculations" sheetId="1" r:id="rId1"/>
@@ -190,12 +190,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -219,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -227,6 +233,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -242,10 +249,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1225,7 +1228,7 @@
         <v>7.1136205146710083E-2</v>
       </c>
       <c r="S14">
-        <f t="shared" ref="S13:S16" si="9">((E14-$L$12)/$L$12)*100</f>
+        <f t="shared" ref="S14:S16" si="9">((E14-$L$12)/$L$12)*100</f>
         <v>-54.084175865299144</v>
       </c>
       <c r="T14">
@@ -3832,7 +3835,7 @@
       <c r="A57">
         <v>29</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C57">
@@ -3923,7 +3926,7 @@
       <c r="A58">
         <v>30</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C58">
@@ -3986,7 +3989,7 @@
       <c r="A59">
         <v>32</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C59">
@@ -4049,7 +4052,7 @@
       <c r="A60">
         <v>33</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C60">
@@ -6561,7 +6564,7 @@
       <c r="A101">
         <v>11</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C101">
@@ -6652,7 +6655,7 @@
       <c r="A102">
         <v>12</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C102">
@@ -6715,7 +6718,7 @@
       <c r="A103">
         <v>14</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C103">
@@ -6778,7 +6781,7 @@
       <c r="A104">
         <v>15</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C104">
@@ -9290,7 +9293,7 @@
       <c r="A145">
         <v>57</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C145" s="1">
@@ -9381,7 +9384,7 @@
       <c r="A146">
         <v>58</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C146" s="1">
@@ -9444,7 +9447,7 @@
       <c r="A147">
         <v>59</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C147" s="1">
@@ -9507,7 +9510,7 @@
       <c r="A148">
         <v>60</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C148" s="1">
